--- a/data/HS_058/HS_058.xlsx
+++ b/data/HS_058/HS_058.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,94 +532,90 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>27</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1952-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>catch_tonnes</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ppr_tonnes</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ppr_over_npp_percent</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C13" t="n">
-        <v>26.138</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4.639</v>
-      </c>
-      <c r="C14" t="n">
-        <v>166.465</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B15" t="n">
-        <v>2.724</v>
+        <v>0.75</v>
       </c>
       <c r="C15" t="n">
-        <v>104.712</v>
+        <v>26.138</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -607,97 +623,97 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="B16" t="n">
-        <v>23.861</v>
+        <v>4.639</v>
       </c>
       <c r="C16" t="n">
-        <v>769.014</v>
+        <v>166.465</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="B17" t="n">
-        <v>97.19499999999999</v>
+        <v>2.724</v>
       </c>
       <c r="C17" t="n">
-        <v>3369.156</v>
+        <v>104.712</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1968</v>
+        <v>1958</v>
       </c>
       <c r="B18" t="n">
-        <v>286.028</v>
+        <v>23.861</v>
       </c>
       <c r="C18" t="n">
-        <v>9036.386</v>
+        <v>769.014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1969</v>
+        <v>1959</v>
       </c>
       <c r="B19" t="n">
-        <v>21.783</v>
+        <v>97.19499999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>1098.176</v>
+        <v>3369.156</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B20" t="n">
-        <v>24.341</v>
+        <v>286.028</v>
       </c>
       <c r="C20" t="n">
-        <v>1239.16</v>
+        <v>9036.386</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B21" t="n">
-        <v>21.559</v>
+        <v>21.783</v>
       </c>
       <c r="C21" t="n">
-        <v>610.754</v>
+        <v>1098.176</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="B22" t="n">
-        <v>0.434</v>
+        <v>24.341</v>
       </c>
       <c r="C22" t="n">
-        <v>11.882</v>
+        <v>1239.16</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -705,349 +721,349 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="B23" t="n">
-        <v>764.926</v>
+        <v>21.559</v>
       </c>
       <c r="C23" t="n">
-        <v>145473.236</v>
+        <v>610.754</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B24" t="n">
-        <v>3499.378</v>
+        <v>0.434</v>
       </c>
       <c r="C24" t="n">
-        <v>664659.518</v>
+        <v>11.882</v>
       </c>
       <c r="D24" t="n">
-        <v>0.137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B25" t="n">
-        <v>6336.52</v>
+        <v>764.926</v>
       </c>
       <c r="C25" t="n">
-        <v>1207272.98</v>
+        <v>145473.236</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2489</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B26" t="n">
-        <v>14830.734</v>
+        <v>3499.378</v>
       </c>
       <c r="C26" t="n">
-        <v>2818661.038</v>
+        <v>664659.518</v>
       </c>
       <c r="D26" t="n">
-        <v>0.581</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B27" t="n">
-        <v>64246.393</v>
+        <v>6336.52</v>
       </c>
       <c r="C27" t="n">
-        <v>12195530.668</v>
+        <v>1207272.98</v>
       </c>
       <c r="D27" t="n">
-        <v>2.514</v>
+        <v>0.0277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B28" t="n">
-        <v>62628.422</v>
+        <v>14830.734</v>
       </c>
       <c r="C28" t="n">
-        <v>11925013.391</v>
+        <v>2818661.038</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4582</v>
+        <v>0.0646</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B29" t="n">
-        <v>118766.274</v>
+        <v>64246.393</v>
       </c>
       <c r="C29" t="n">
-        <v>22621961.424</v>
+        <v>12195530.668</v>
       </c>
       <c r="D29" t="n">
-        <v>4.6633</v>
+        <v>0.2793</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B30" t="n">
-        <v>161313.268</v>
+        <v>62628.422</v>
       </c>
       <c r="C30" t="n">
-        <v>30788077.591</v>
+        <v>11925013.391</v>
       </c>
       <c r="D30" t="n">
-        <v>6.3467</v>
+        <v>0.2731</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B31" t="n">
-        <v>146798.012</v>
+        <v>118766.274</v>
       </c>
       <c r="C31" t="n">
-        <v>27965048.867</v>
+        <v>22621961.424</v>
       </c>
       <c r="D31" t="n">
-        <v>5.7647</v>
+        <v>0.5181</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B32" t="n">
-        <v>77742.554</v>
+        <v>161313.268</v>
       </c>
       <c r="C32" t="n">
-        <v>14723765.905</v>
+        <v>30788077.591</v>
       </c>
       <c r="D32" t="n">
-        <v>3.0352</v>
+        <v>0.7052</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B33" t="n">
-        <v>25178.664</v>
+        <v>146798.012</v>
       </c>
       <c r="C33" t="n">
-        <v>4582010.988</v>
+        <v>27965048.867</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9445</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B34" t="n">
-        <v>10116.25</v>
+        <v>77742.554</v>
       </c>
       <c r="C34" t="n">
-        <v>1539858.774</v>
+        <v>14723765.905</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3174</v>
+        <v>0.3372</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B35" t="n">
-        <v>29401.198</v>
+        <v>25178.664</v>
       </c>
       <c r="C35" t="n">
-        <v>5126812.289</v>
+        <v>4582010.988</v>
       </c>
       <c r="D35" t="n">
-        <v>1.0568</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B36" t="n">
-        <v>31929.999</v>
+        <v>10116.25</v>
       </c>
       <c r="C36" t="n">
-        <v>5868698.22</v>
+        <v>1539858.774</v>
       </c>
       <c r="D36" t="n">
-        <v>1.2098</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B37" t="n">
-        <v>12631.212</v>
+        <v>29401.198</v>
       </c>
       <c r="C37" t="n">
-        <v>2040363.138</v>
+        <v>5126812.289</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4206</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B38" t="n">
-        <v>7504.5</v>
+        <v>31929.999</v>
       </c>
       <c r="C38" t="n">
-        <v>1414215.258</v>
+        <v>5868698.22</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2915</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B39" t="n">
-        <v>33355.5</v>
+        <v>12631.212</v>
       </c>
       <c r="C39" t="n">
-        <v>5736903.056</v>
+        <v>2040363.138</v>
       </c>
       <c r="D39" t="n">
-        <v>1.1826</v>
+        <v>0.0467</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B40" t="n">
-        <v>2338.973</v>
+        <v>7504.5</v>
       </c>
       <c r="C40" t="n">
-        <v>466521.118</v>
+        <v>1414215.258</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B41" t="n">
-        <v>13.106</v>
+        <v>33355.5</v>
       </c>
       <c r="C41" t="n">
-        <v>2480.985</v>
+        <v>5736903.056</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B42" t="n">
-        <v>5750.034</v>
+        <v>2338.973</v>
       </c>
       <c r="C42" t="n">
-        <v>1095485.599</v>
+        <v>466521.118</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2258</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B43" t="n">
-        <v>899</v>
+        <v>13.106</v>
       </c>
       <c r="C43" t="n">
-        <v>171300.919</v>
+        <v>2480.985</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0353</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B44" t="n">
-        <v>1266</v>
+        <v>5750.034</v>
       </c>
       <c r="C44" t="n">
-        <v>241231.327</v>
+        <v>1095485.599</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0497</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B45" t="n">
-        <v>6.85</v>
+        <v>899</v>
       </c>
       <c r="C45" t="n">
-        <v>46.078</v>
+        <v>171300.919</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B46" t="n">
-        <v>5.938</v>
+        <v>1266</v>
       </c>
       <c r="C46" t="n">
-        <v>609.268</v>
+        <v>241231.327</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B47" t="n">
-        <v>3.873</v>
+        <v>6.85</v>
       </c>
       <c r="C47" t="n">
-        <v>180.83</v>
+        <v>46.078</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1055,41 +1071,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B48" t="n">
-        <v>4.21</v>
+        <v>5.938</v>
       </c>
       <c r="C48" t="n">
-        <v>461.031</v>
+        <v>609.268</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B49" t="n">
-        <v>178.335</v>
+        <v>3.873</v>
       </c>
       <c r="C49" t="n">
-        <v>85212.285</v>
+        <v>180.83</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B50" t="n">
-        <v>11.89</v>
+        <v>4.21</v>
       </c>
       <c r="C50" t="n">
-        <v>81.935</v>
+        <v>461.031</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1097,254 +1113,289 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B51" t="n">
-        <v>0.064</v>
+        <v>178.335</v>
       </c>
       <c r="C51" t="n">
-        <v>2.306</v>
+        <v>85212.285</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B52" t="n">
-        <v>236.133</v>
+        <v>11.89</v>
       </c>
       <c r="C52" t="n">
-        <v>44888.289</v>
+        <v>81.935</v>
       </c>
       <c r="D52" t="n">
-        <v>0.009299999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B53" t="n">
-        <v>400.71</v>
+        <v>0.064</v>
       </c>
       <c r="C53" t="n">
-        <v>71155.796</v>
+        <v>2.306</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B54" t="n">
-        <v>1306.204</v>
+        <v>236.133</v>
       </c>
       <c r="C54" t="n">
-        <v>230934.527</v>
+        <v>44888.289</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0476</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B55" t="n">
-        <v>1870.644</v>
+        <v>400.71</v>
       </c>
       <c r="C55" t="n">
-        <v>358126.69</v>
+        <v>71155.796</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0738</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B56" t="n">
-        <v>1926.493</v>
+        <v>1306.204</v>
       </c>
       <c r="C56" t="n">
-        <v>367343.099</v>
+        <v>230934.527</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0757</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B57" t="n">
-        <v>978.0839999999999</v>
+        <v>1870.644</v>
       </c>
       <c r="C57" t="n">
-        <v>228743.011</v>
+        <v>358126.69</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0472</v>
+        <v>0.008200000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B58" t="n">
-        <v>798.826</v>
+        <v>1926.493</v>
       </c>
       <c r="C58" t="n">
-        <v>152982.523</v>
+        <v>367343.099</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0315</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B59" t="n">
-        <v>1681.743</v>
+        <v>978.0839999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>356460.918</v>
+        <v>228743.011</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0735</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B60" t="n">
-        <v>1758.914</v>
+        <v>798.826</v>
       </c>
       <c r="C60" t="n">
-        <v>360603.931</v>
+        <v>152982.523</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0743</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B61" t="n">
-        <v>1663.848</v>
+        <v>1681.743</v>
       </c>
       <c r="C61" t="n">
-        <v>337465.999</v>
+        <v>356460.918</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0696</v>
+        <v>0.008200000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B62" t="n">
-        <v>1451.293</v>
+        <v>1758.914</v>
       </c>
       <c r="C62" t="n">
-        <v>298970.836</v>
+        <v>360603.931</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0616</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B63" t="n">
-        <v>1542.088</v>
+        <v>1663.848</v>
       </c>
       <c r="C63" t="n">
-        <v>313259.573</v>
+        <v>337465.999</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0646</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B64" t="n">
-        <v>1506.876</v>
+        <v>1451.293</v>
       </c>
       <c r="C64" t="n">
-        <v>312140.549</v>
+        <v>298970.836</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0643</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B65" t="n">
-        <v>2383.226</v>
+        <v>1542.088</v>
       </c>
       <c r="C65" t="n">
-        <v>484294.066</v>
+        <v>313259.573</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0998</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B66" t="n">
-        <v>2468.59</v>
+        <v>1506.876</v>
       </c>
       <c r="C66" t="n">
-        <v>492987.911</v>
+        <v>312140.549</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1016</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B67" t="n">
-        <v>1949.486</v>
+        <v>2383.226</v>
       </c>
       <c r="C67" t="n">
-        <v>372910.086</v>
+        <v>484294.066</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0769</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2468.59</v>
+      </c>
+      <c r="C68" t="n">
+        <v>492987.911</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.0113</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1949.486</v>
+      </c>
+      <c r="C69" t="n">
+        <v>372910.086</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
         <v>2019</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B70" t="n">
         <v>1622.28</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C70" t="n">
         <v>316826.047</v>
       </c>
-      <c r="D68" t="n">
-        <v>0.0653</v>
+      <c r="D70" t="n">
+        <v>0.0073</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1444,285 +1495,173 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AY1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AZ1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BA1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BB1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BC1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BD1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BE1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BF1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BG1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BH1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1968</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AZ1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BA1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BB1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BC1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BD1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BE1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BF1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BG1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BH1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -7005,6 +6944,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7155,285 +7333,173 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1954</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1959</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -8509,7 +8575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/HS_058/HS_058.xlsx
+++ b/data/HS_058/HS_058.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$59</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,9 +620,6 @@
       <c r="C15" t="n">
         <v>26.138</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -631,9 +631,6 @@
       <c r="C16" t="n">
         <v>166.465</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -645,9 +642,6 @@
       <c r="C17" t="n">
         <v>104.712</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -659,9 +653,6 @@
       <c r="C18" t="n">
         <v>769.014</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -673,9 +664,6 @@
       <c r="C19" t="n">
         <v>3369.156</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.0001</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -687,9 +675,6 @@
       <c r="C20" t="n">
         <v>9036.386</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.0002</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -701,9 +686,6 @@
       <c r="C21" t="n">
         <v>1098.176</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -715,9 +697,6 @@
       <c r="C22" t="n">
         <v>1239.16</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -729,9 +708,6 @@
       <c r="C23" t="n">
         <v>610.754</v>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -743,9 +719,6 @@
       <c r="C24" t="n">
         <v>11.882</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -757,9 +730,6 @@
       <c r="C25" t="n">
         <v>145473.236</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.0033</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -771,9 +741,6 @@
       <c r="C26" t="n">
         <v>664659.518</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.0152</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -785,9 +752,6 @@
       <c r="C27" t="n">
         <v>1207272.98</v>
       </c>
-      <c r="D27" t="n">
-        <v>0.0277</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -799,9 +763,6 @@
       <c r="C28" t="n">
         <v>2818661.038</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.0646</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -813,9 +774,6 @@
       <c r="C29" t="n">
         <v>12195530.668</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.2793</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -827,9 +785,6 @@
       <c r="C30" t="n">
         <v>11925013.391</v>
       </c>
-      <c r="D30" t="n">
-        <v>0.2731</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -841,9 +796,6 @@
       <c r="C31" t="n">
         <v>22621961.424</v>
       </c>
-      <c r="D31" t="n">
-        <v>0.5181</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -855,9 +807,6 @@
       <c r="C32" t="n">
         <v>30788077.591</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.7052</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -869,9 +818,6 @@
       <c r="C33" t="n">
         <v>27965048.867</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.6405</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -883,9 +829,6 @@
       <c r="C34" t="n">
         <v>14723765.905</v>
       </c>
-      <c r="D34" t="n">
-        <v>0.3372</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -897,9 +840,6 @@
       <c r="C35" t="n">
         <v>4582010.988</v>
       </c>
-      <c r="D35" t="n">
-        <v>0.1049</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -911,9 +851,6 @@
       <c r="C36" t="n">
         <v>1539858.774</v>
       </c>
-      <c r="D36" t="n">
-        <v>0.0353</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -925,9 +862,6 @@
       <c r="C37" t="n">
         <v>5126812.289</v>
       </c>
-      <c r="D37" t="n">
-        <v>0.1174</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -939,9 +873,6 @@
       <c r="C38" t="n">
         <v>5868698.22</v>
       </c>
-      <c r="D38" t="n">
-        <v>0.1344</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -953,9 +884,6 @@
       <c r="C39" t="n">
         <v>2040363.138</v>
       </c>
-      <c r="D39" t="n">
-        <v>0.0467</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -967,9 +895,6 @@
       <c r="C40" t="n">
         <v>1414215.258</v>
       </c>
-      <c r="D40" t="n">
-        <v>0.0324</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -981,9 +906,6 @@
       <c r="C41" t="n">
         <v>5736903.056</v>
       </c>
-      <c r="D41" t="n">
-        <v>0.1314</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -995,9 +917,6 @@
       <c r="C42" t="n">
         <v>466521.118</v>
       </c>
-      <c r="D42" t="n">
-        <v>0.0107</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1009,9 +928,6 @@
       <c r="C43" t="n">
         <v>2480.985</v>
       </c>
-      <c r="D43" t="n">
-        <v>0.0001</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1023,9 +939,6 @@
       <c r="C44" t="n">
         <v>1095485.599</v>
       </c>
-      <c r="D44" t="n">
-        <v>0.0251</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1037,9 +950,6 @@
       <c r="C45" t="n">
         <v>171300.919</v>
       </c>
-      <c r="D45" t="n">
-        <v>0.0039</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1051,9 +961,6 @@
       <c r="C46" t="n">
         <v>241231.327</v>
       </c>
-      <c r="D46" t="n">
-        <v>0.0055</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1065,9 +972,6 @@
       <c r="C47" t="n">
         <v>46.078</v>
       </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1079,9 +983,6 @@
       <c r="C48" t="n">
         <v>609.268</v>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1122,7 +1023,7 @@
         <v>85212.285</v>
       </c>
       <c r="D51" t="n">
-        <v>0.002</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="52">
@@ -1164,7 +1065,7 @@
         <v>44888.289</v>
       </c>
       <c r="D54" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="55">
@@ -1178,7 +1079,7 @@
         <v>71155.796</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0016</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="56">
@@ -1192,7 +1093,7 @@
         <v>230934.527</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0053</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="57">
@@ -1206,7 +1107,7 @@
         <v>358126.69</v>
       </c>
       <c r="D57" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="58">
@@ -1220,7 +1121,7 @@
         <v>367343.099</v>
       </c>
       <c r="D58" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="59">
@@ -1234,7 +1135,7 @@
         <v>228743.011</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0052</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="60">
@@ -1248,7 +1149,7 @@
         <v>152982.523</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="61">
@@ -1262,7 +1163,7 @@
         <v>356460.918</v>
       </c>
       <c r="D61" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="62">
@@ -1276,7 +1177,7 @@
         <v>360603.931</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0083</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="63">
@@ -1290,7 +1191,7 @@
         <v>337465.999</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0077</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="64">
@@ -1304,7 +1205,7 @@
         <v>298970.836</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0068</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="65">
@@ -1318,7 +1219,7 @@
         <v>313259.573</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0072</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="66">
@@ -1332,7 +1233,7 @@
         <v>312140.549</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0071</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="67">
@@ -1346,7 +1247,7 @@
         <v>484294.066</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0111</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1360,7 +1261,7 @@
         <v>492987.911</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0113</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -1374,7 +1275,7 @@
         <v>372910.086</v>
       </c>
       <c r="D69" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="70">
@@ -1388,17 +1289,1987 @@
         <v>316826.047</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0073</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1952</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1970</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1971</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1983</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1986</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B38" t="n">
+        <v>576791220.7017887</v>
+      </c>
+      <c r="G38" t="n">
+        <v>576791220.7017887</v>
+      </c>
+      <c r="H38" t="n">
+        <v>576791220.7017887</v>
+      </c>
+      <c r="I38" t="n">
+        <v>576791220.7017887</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B39" t="n">
+        <v>609951055.3570309</v>
+      </c>
+      <c r="G39" t="n">
+        <v>609951055.3570309</v>
+      </c>
+      <c r="H39" t="n">
+        <v>609951055.3570309</v>
+      </c>
+      <c r="I39" t="n">
+        <v>609951055.3570309</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B40" t="n">
+        <v>631240331.5623258</v>
+      </c>
+      <c r="G40" t="n">
+        <v>631240331.5623258</v>
+      </c>
+      <c r="H40" t="n">
+        <v>631240331.5623258</v>
+      </c>
+      <c r="I40" t="n">
+        <v>631240331.5623258</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>592667705.9751402</v>
+      </c>
+      <c r="G41" t="n">
+        <v>592667705.9751402</v>
+      </c>
+      <c r="H41" t="n">
+        <v>592667705.9751402</v>
+      </c>
+      <c r="I41" t="n">
+        <v>592667705.9751402</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B42" t="n">
+        <v>554270735.7918217</v>
+      </c>
+      <c r="G42" t="n">
+        <v>554270735.7918217</v>
+      </c>
+      <c r="H42" t="n">
+        <v>554270735.7918217</v>
+      </c>
+      <c r="I42" t="n">
+        <v>554270735.7918217</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B43" t="n">
+        <v>568307435.4834158</v>
+      </c>
+      <c r="C43" t="n">
+        <v>414724975.8104656</v>
+      </c>
+      <c r="D43" t="n">
+        <v>321489591.1696243</v>
+      </c>
+      <c r="E43" t="n">
+        <v>651830736.901624</v>
+      </c>
+      <c r="F43" t="n">
+        <v>969467136.6420476</v>
+      </c>
+      <c r="G43" t="n">
+        <v>568307435.4834158</v>
+      </c>
+      <c r="H43" t="n">
+        <v>321489591.1696243</v>
+      </c>
+      <c r="I43" t="n">
+        <v>969467136.6420476</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B44" t="n">
+        <v>576778361.8755263</v>
+      </c>
+      <c r="C44" t="n">
+        <v>412605174.3634464</v>
+      </c>
+      <c r="D44" t="n">
+        <v>325408436.9614937</v>
+      </c>
+      <c r="E44" t="n">
+        <v>671297842.4388345</v>
+      </c>
+      <c r="F44" t="n">
+        <v>950106710.9579492</v>
+      </c>
+      <c r="G44" t="n">
+        <v>576778361.8755263</v>
+      </c>
+      <c r="H44" t="n">
+        <v>325408436.9614937</v>
+      </c>
+      <c r="I44" t="n">
+        <v>950106710.9579492</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B45" t="n">
+        <v>551673664.4467981</v>
+      </c>
+      <c r="C45" t="n">
+        <v>396439682.285882</v>
+      </c>
+      <c r="D45" t="n">
+        <v>305450868.6341826</v>
+      </c>
+      <c r="E45" t="n">
+        <v>634599318.2775142</v>
+      </c>
+      <c r="F45" t="n">
+        <v>901250946.2534257</v>
+      </c>
+      <c r="G45" t="n">
+        <v>551673664.4467981</v>
+      </c>
+      <c r="H45" t="n">
+        <v>305450868.6341826</v>
+      </c>
+      <c r="I45" t="n">
+        <v>901250946.2534257</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B46" t="n">
+        <v>576713960.1836644</v>
+      </c>
+      <c r="C46" t="n">
+        <v>414394622.4037297</v>
+      </c>
+      <c r="D46" t="n">
+        <v>326649364.0541169</v>
+      </c>
+      <c r="E46" t="n">
+        <v>672040089.0568208</v>
+      </c>
+      <c r="F46" t="n">
+        <v>916844061.0909511</v>
+      </c>
+      <c r="G46" t="n">
+        <v>576713960.1836644</v>
+      </c>
+      <c r="H46" t="n">
+        <v>326649364.0541169</v>
+      </c>
+      <c r="I46" t="n">
+        <v>916844061.0909511</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>5</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B47" t="n">
+        <v>578183358.9545654</v>
+      </c>
+      <c r="C47" t="n">
+        <v>413580150.0146458</v>
+      </c>
+      <c r="D47" t="n">
+        <v>326851947.907847</v>
+      </c>
+      <c r="E47" t="n">
+        <v>702503185.2403666</v>
+      </c>
+      <c r="F47" t="n">
+        <v>903348677.1834948</v>
+      </c>
+      <c r="G47" t="n">
+        <v>578183358.9545654</v>
+      </c>
+      <c r="H47" t="n">
+        <v>326851947.907847</v>
+      </c>
+      <c r="I47" t="n">
+        <v>903348677.1834948</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B48" t="n">
+        <v>565533705.120615</v>
+      </c>
+      <c r="C48" t="n">
+        <v>413430800.7883134</v>
+      </c>
+      <c r="D48" t="n">
+        <v>320989118.9264024</v>
+      </c>
+      <c r="E48" t="n">
+        <v>663765082.3742151</v>
+      </c>
+      <c r="F48" t="n">
+        <v>917453635.1173021</v>
+      </c>
+      <c r="G48" t="n">
+        <v>565533705.120615</v>
+      </c>
+      <c r="H48" t="n">
+        <v>320989118.9264024</v>
+      </c>
+      <c r="I48" t="n">
+        <v>917453635.1173021</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B49" t="n">
+        <v>583517492.415159</v>
+      </c>
+      <c r="C49" t="n">
+        <v>432793800.6418695</v>
+      </c>
+      <c r="D49" t="n">
+        <v>337693028.3617247</v>
+      </c>
+      <c r="E49" t="n">
+        <v>685965767.4136649</v>
+      </c>
+      <c r="F49" t="n">
+        <v>958602466.8827147</v>
+      </c>
+      <c r="G49" t="n">
+        <v>583517492.415159</v>
+      </c>
+      <c r="H49" t="n">
+        <v>337693028.3617247</v>
+      </c>
+      <c r="I49" t="n">
+        <v>958602466.8827147</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>5</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B50" t="n">
+        <v>614953015.5526047</v>
+      </c>
+      <c r="C50" t="n">
+        <v>456633807.0668138</v>
+      </c>
+      <c r="D50" t="n">
+        <v>360757410.10943</v>
+      </c>
+      <c r="E50" t="n">
+        <v>684605591.8918605</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1020019973.987828</v>
+      </c>
+      <c r="G50" t="n">
+        <v>614953015.5526047</v>
+      </c>
+      <c r="H50" t="n">
+        <v>360757410.10943</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1020019973.987828</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B51" t="n">
+        <v>606843311.5454611</v>
+      </c>
+      <c r="C51" t="n">
+        <v>447163351.8012599</v>
+      </c>
+      <c r="D51" t="n">
+        <v>356621233.6912813</v>
+      </c>
+      <c r="E51" t="n">
+        <v>728076372.7643123</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1018752311.189034</v>
+      </c>
+      <c r="G51" t="n">
+        <v>606843311.5454611</v>
+      </c>
+      <c r="H51" t="n">
+        <v>356621233.6912813</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1018752311.189034</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B52" t="n">
+        <v>557734723.1710125</v>
+      </c>
+      <c r="C52" t="n">
+        <v>419712559.1827005</v>
+      </c>
+      <c r="D52" t="n">
+        <v>327014131.8726161</v>
+      </c>
+      <c r="E52" t="n">
+        <v>640941002.6367506</v>
+      </c>
+      <c r="F52" t="n">
+        <v>957516497.7600111</v>
+      </c>
+      <c r="G52" t="n">
+        <v>557734723.1710125</v>
+      </c>
+      <c r="H52" t="n">
+        <v>327014131.8726161</v>
+      </c>
+      <c r="I52" t="n">
+        <v>957516497.7600111</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>5</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B53" t="n">
+        <v>538213496.7426584</v>
+      </c>
+      <c r="C53" t="n">
+        <v>414405314.2213424</v>
+      </c>
+      <c r="D53" t="n">
+        <v>317139954.8818148</v>
+      </c>
+      <c r="E53" t="n">
+        <v>637737122.7281227</v>
+      </c>
+      <c r="F53" t="n">
+        <v>931938074.8166765</v>
+      </c>
+      <c r="G53" t="n">
+        <v>538213496.7426584</v>
+      </c>
+      <c r="H53" t="n">
+        <v>317139954.8818148</v>
+      </c>
+      <c r="I53" t="n">
+        <v>931938074.8166765</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>5</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B54" t="n">
+        <v>572953792.6782639</v>
+      </c>
+      <c r="C54" t="n">
+        <v>433156748.5661295</v>
+      </c>
+      <c r="D54" t="n">
+        <v>339061716.1869973</v>
+      </c>
+      <c r="E54" t="n">
+        <v>620046987.421163</v>
+      </c>
+      <c r="F54" t="n">
+        <v>969732684.8772068</v>
+      </c>
+      <c r="G54" t="n">
+        <v>572953792.6782639</v>
+      </c>
+      <c r="H54" t="n">
+        <v>339061716.1869973</v>
+      </c>
+      <c r="I54" t="n">
+        <v>969732684.8772068</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>5</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B55" t="n">
+        <v>584957665.3543561</v>
+      </c>
+      <c r="C55" t="n">
+        <v>441659575.3092469</v>
+      </c>
+      <c r="D55" t="n">
+        <v>353022303.8104403</v>
+      </c>
+      <c r="E55" t="n">
+        <v>608199739.2771416</v>
+      </c>
+      <c r="F55" t="n">
+        <v>913692943.1496879</v>
+      </c>
+      <c r="G55" t="n">
+        <v>584957665.3543561</v>
+      </c>
+      <c r="H55" t="n">
+        <v>353022303.8104403</v>
+      </c>
+      <c r="I55" t="n">
+        <v>913692943.1496879</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B56" t="n">
+        <v>599017430.026355</v>
+      </c>
+      <c r="C56" t="n">
+        <v>469804317.0391195</v>
+      </c>
+      <c r="D56" t="n">
+        <v>374243669.3431643</v>
+      </c>
+      <c r="E56" t="n">
+        <v>659158641.1732293</v>
+      </c>
+      <c r="F56" t="n">
+        <v>956528255.5163827</v>
+      </c>
+      <c r="G56" t="n">
+        <v>599017430.026355</v>
+      </c>
+      <c r="H56" t="n">
+        <v>374243669.3431643</v>
+      </c>
+      <c r="I56" t="n">
+        <v>956528255.5163827</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>5</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B57" t="n">
+        <v>550978714.9931087</v>
+      </c>
+      <c r="C57" t="n">
+        <v>472047187.7690695</v>
+      </c>
+      <c r="D57" t="n">
+        <v>359313300.5940546</v>
+      </c>
+      <c r="E57" t="n">
+        <v>631663882.3022555</v>
+      </c>
+      <c r="F57" t="n">
+        <v>964686177.5392278</v>
+      </c>
+      <c r="G57" t="n">
+        <v>550978714.9931087</v>
+      </c>
+      <c r="H57" t="n">
+        <v>359313300.5940546</v>
+      </c>
+      <c r="I57" t="n">
+        <v>964686177.5392278</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B58" t="n">
+        <v>555585095.4443878</v>
+      </c>
+      <c r="C58" t="n">
+        <v>457988235.2312801</v>
+      </c>
+      <c r="D58" t="n">
+        <v>355737990.8188043</v>
+      </c>
+      <c r="E58" t="n">
+        <v>677528364.2265404</v>
+      </c>
+      <c r="F58" t="n">
+        <v>977633260.3337731</v>
+      </c>
+      <c r="G58" t="n">
+        <v>555585095.4443878</v>
+      </c>
+      <c r="H58" t="n">
+        <v>355737990.8188043</v>
+      </c>
+      <c r="I58" t="n">
+        <v>977633260.3337731</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B59" t="n">
+        <v>542531200.6909659</v>
+      </c>
+      <c r="C59" t="n">
+        <v>449621979.587157</v>
+      </c>
+      <c r="D59" t="n">
+        <v>349226049.0451434</v>
+      </c>
+      <c r="E59" t="n">
+        <v>746585952.2254945</v>
+      </c>
+      <c r="F59" t="n">
+        <v>994300822.5438255</v>
+      </c>
+      <c r="G59" t="n">
+        <v>542531200.6909659</v>
+      </c>
+      <c r="H59" t="n">
+        <v>349226049.0451434</v>
+      </c>
+      <c r="I59" t="n">
+        <v>994300822.5438255</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>5</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6805,136 +8676,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for HS_058</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dissostichus eleginoides</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="C5" t="n">
-        <v>912.010839</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chionobathyscus dewitti</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="C6" t="n">
-        <v>575.439937</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trematomus eulepidotus</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C9" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Artedidraconidae</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>125.892541</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -6949,43 +8707,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for HS_058</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Dissostichus eleginoides</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="C5" t="n">
+        <v>912.010839</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chionobathyscus dewitti</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="C6" t="n">
+        <v>575.439937</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Trematomus eulepidotus</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C9" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Artedidraconidae</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>125.892541</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -7010,14 +8861,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -7061,14 +8912,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -7097,6 +8948,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7182,7 +9084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8573,132 +10475,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Net primary production, 2019, tonnes carbon per year</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>satellite_model</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>npp_tC_yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antoine-Morel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>485107082.7267168</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGPM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>402031821.5238997</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eppley</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>312262280.3051776</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CbPM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>667563695.5581428</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAFE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>889059229.7045785</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ensemble median</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>485107082.7267168</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ensemble min</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>312262280.3051776</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ensemble max</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>889059229.7045785</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>water area (km2)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>10660106.0370015</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>